--- a/data/trans_orig/IP31KM13_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM13_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>116316</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>110965</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>119133</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>95,96%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>91496</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>84085</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>95814</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89,96%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>82,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>129673</t>
+          <t>90022</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123810</t>
+          <t>83143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132779</t>
+          <t>94424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>221170</t>
+          <t>206338</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>212886</t>
+          <t>197884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227168</t>
+          <t>211765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10244</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10213</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5895</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17624</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15716</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>78110</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72378</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>82960</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>86,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>80,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>86703</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>82196</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>90276</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>92,84%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>88,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81756</t>
+          <t>88613</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75196</t>
+          <t>83209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86687</t>
+          <t>92296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>168460</t>
+          <t>166724</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159497</t>
+          <t>158791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174665</t>
+          <t>172817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11770</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6920</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17502</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6689</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3116</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11196</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27604</t>
+          <t>26499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51789</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46723</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>54402</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>48853</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>45636</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>50796</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>47308</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>90,96%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>57446</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>51988</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>60482</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>92,16%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>83,4%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>143</t>
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>106298</t>
+          <t>102585</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100316</t>
+          <t>97320</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109693</t>
+          <t>105336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4055</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4453</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4888</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1852</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>10346</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>182796</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>174306</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>188508</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>92,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>88,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>95,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>202529</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>194286</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>208162</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>196991</t>
+          <t>163231</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189208</t>
+          <t>155559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202791</t>
+          <t>169138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>399521</t>
+          <t>346027</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>389231</t>
+          <t>335305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>408666</t>
+          <t>353653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14517</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8805</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23007</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>13008</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7375</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21251</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>28675</t>
+          <t>27926</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>126279</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>100099</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>136896</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>86,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>68,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>94,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>102770</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>91353</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>108343</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>88,97%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>79,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>93,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>138311</t>
+          <t>105443</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105477</t>
+          <t>99392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150935</t>
+          <t>109930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>241081</t>
+          <t>231722</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206975</t>
+          <t>203520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255038</t>
+          <t>243037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19307</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8690</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>45487</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>31,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>12739</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7166</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24156</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21150</t>
+          <t>10023</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53984</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>33889</t>
+          <t>29330</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19932</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67995</t>
+          <t>57532</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,74 +2435,74 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>59592</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>53755</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>63299</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>62799</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>57812</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>65971</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>91,15%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>83,91%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>63721</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>58071</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>67372</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>82,54%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>95,76%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>62651</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>56900</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>65854</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>82,43%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>167</t>
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>125449</t>
+          <t>123314</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>118283</t>
+          <t>115833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130397</t>
+          <t>128845</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2564</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12108</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>6096</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2924</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11083</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>6635</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2984</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>12285</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>4,24%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>16,09%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>6380</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>3177</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>12131</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>12906</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>614882</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>582290</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>629584</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>86,18%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>93,18%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>833</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>595150</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>580276</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>607161</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>89,95%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>852</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>666828</t>
+          <t>561827</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>630628</t>
+          <t>550295</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>682913</t>
+          <t>572806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1261978</t>
+          <t>1176710</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1226029</t>
+          <t>1147492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1281456</t>
+          <t>1195512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>60813</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>46111</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>93405</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>13,82%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>49981</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>37970</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>64855</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>48405</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49455</t>
+          <t>37426</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>101740</t>
+          <t>59937</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>115521</t>
+          <t>109217</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96043</t>
+          <t>90415</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>151470</t>
+          <t>138435</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
